--- a/output/pdf_financials_xlsx/CCL.A.xlsx
+++ b/output/pdf_financials_xlsx/CCL.A.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>136.269</v>
+        <v>57.937</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>150.594</v>
+        <v>74.02200000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>214.601</v>
+        <v>136.269</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>227.166</v>
+        <v>150.594</v>
       </c>
     </row>
     <row r="37">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>114.614</v>
+        <v>192.946</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>131.625</v>
+        <v>208.197</v>
       </c>
     </row>
     <row r="49">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
